--- a/Forest字典.xlsx
+++ b/Forest字典.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="84">
   <si>
     <t>UA名字</t>
   </si>
@@ -281,6 +281,9 @@
   </si>
   <si>
     <t>9133</t>
+  </si>
+  <si>
+    <t>6490</t>
   </si>
 </sst>
 </file>
@@ -293,7 +296,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -311,20 +314,6 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -792,19 +781,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -813,127 +811,118 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -946,7 +935,7 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1268,7 +1257,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B75"/>
+  <dimension ref="A1:B76"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -1867,11 +1856,19 @@
       </c>
     </row>
     <row r="75" spans="1:2">
-      <c r="A75" s="4" t="s">
+      <c r="A75" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B75" s="4" t="s">
+      <c r="B75" s="2" t="s">
         <v>82</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
